--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="250">
   <si>
     <t>Name</t>
   </si>
@@ -118,7 +118,7 @@
     <t>RELX Creator Pro Device (2)</t>
   </si>
   <si>
-    <t>12138.0</t>
+    <t>12133.0</t>
   </si>
   <si>
     <t>RELX Creator Pro Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>1390.0</t>
+    <t>1385.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>9568.0</t>
+    <t>11768.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -253,7 +253,7 @@
     <t>RELX MagicGo GA4000 (GA06B) (10)</t>
   </si>
   <si>
-    <t>5773.0</t>
+    <t>5743.0</t>
   </si>
   <si>
     <t>RELX MagicGo GA4000 (GA06B)</t>
@@ -361,7 +361,7 @@
     <t>RELX Pocket (G01BC) (6)</t>
   </si>
   <si>
-    <t>915.0</t>
+    <t>913.0</t>
   </si>
   <si>
     <t>RELX Pocket (G01BC)</t>
@@ -382,7 +382,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>20620.0</t>
+    <t>43120.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -565,10 +565,10 @@
     <t>Oolong Ice Tea|高凉铁观音</t>
   </si>
   <si>
-    <t>RELX Pod Pro 2-3 Pods (58)</t>
-  </si>
-  <si>
-    <t>166644.0</t>
+    <t>RELX Pod Pro 2-3 Pods (57)</t>
+  </si>
+  <si>
+    <t>166494.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -676,9 +676,6 @@
     <t>Pineapple Ice|菠萝</t>
   </si>
   <si>
-    <t>Iced Pocary Sweat|宝矿力</t>
-  </si>
-  <si>
     <t>Pear Loquat|秋月枇杷梨</t>
   </si>
   <si>
@@ -742,7 +739,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>52245.0</t>
+    <t>52235.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1122,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="30.7109375" customWidth="1"/>
@@ -1449,7 +1446,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <v>6040</v>
+        <v>6035</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1480,7 +1477,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1740,7 +1737,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>1524</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1751,7 +1748,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1784,7 +1781,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>582</v>
+        <v>982</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1806,7 +1803,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1189</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1837,7 +1834,7 @@
         <v>81</v>
       </c>
       <c r="C66" s="3">
-        <v>896</v>
+        <v>866</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2185,7 +2182,7 @@
         <v>42</v>
       </c>
       <c r="C98" s="3">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2196,7 +2193,7 @@
         <v>41</v>
       </c>
       <c r="C99" s="3">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2370,7 +2367,7 @@
         <v>134</v>
       </c>
       <c r="C115" s="3">
-        <v>1940</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -2403,7 +2400,7 @@
         <v>137</v>
       </c>
       <c r="C118" s="3">
-        <v>0</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2436,7 +2433,7 @@
         <v>140</v>
       </c>
       <c r="C121" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2469,7 +2466,7 @@
         <v>143</v>
       </c>
       <c r="C124" s="3">
-        <v>1800</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2843,7 +2840,7 @@
         <v>177</v>
       </c>
       <c r="C158" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2887,7 +2884,7 @@
         <v>181</v>
       </c>
       <c r="C162" s="3">
-        <v>2120</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -2962,7 +2959,7 @@
         <v>189</v>
       </c>
       <c r="C169" s="3">
-        <v>980</v>
+        <v>940</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -3050,7 +3047,7 @@
         <v>195</v>
       </c>
       <c r="C177" s="3">
-        <v>5390</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3061,7 +3058,7 @@
         <v>196</v>
       </c>
       <c r="C178" s="3">
-        <v>3890</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3369,7 +3366,7 @@
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3380,7 +3377,7 @@
         <v>221</v>
       </c>
       <c r="C207" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -3391,7 +3388,7 @@
         <v>222</v>
       </c>
       <c r="C208" s="3">
-        <v>0</v>
+        <v>516</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -3402,7 +3399,7 @@
         <v>223</v>
       </c>
       <c r="C209" s="3">
-        <v>516</v>
+        <v>819</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -3413,7 +3410,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3432,10 +3429,10 @@
         <v>185</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>226</v>
+        <v>53</v>
       </c>
       <c r="C212" s="3">
-        <v>0</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -3443,10 +3440,10 @@
         <v>185</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="C213" s="3">
-        <v>2385</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -3457,7 +3454,7 @@
         <v>227</v>
       </c>
       <c r="C214" s="3">
-        <v>3615</v>
+        <v>6919</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3468,7 +3465,7 @@
         <v>228</v>
       </c>
       <c r="C215" s="3">
-        <v>6919</v>
+        <v>780</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -3476,10 +3473,10 @@
         <v>185</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>229</v>
+        <v>127</v>
       </c>
       <c r="C216" s="3">
-        <v>780</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -3487,10 +3484,10 @@
         <v>185</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="C217" s="3">
-        <v>2560</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3501,7 +3498,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="3">
-        <v>0</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3512,7 +3509,7 @@
         <v>231</v>
       </c>
       <c r="C219" s="3">
-        <v>1213</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -3523,7 +3520,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="3">
-        <v>9780</v>
+        <v>8175</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -3534,32 +3531,32 @@
         <v>233</v>
       </c>
       <c r="C221" s="3">
-        <v>8205</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B222" s="3" t="s">
+      <c r="A222" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C222" s="3">
-        <v>8360</v>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B223" s="2"/>
-      <c r="C223" s="2" t="s">
+      <c r="A223" s="3" t="s">
         <v>236</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C223" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>238</v>
@@ -3570,7 +3567,7 @@
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>239</v>
@@ -3580,141 +3577,141 @@
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B226" s="3" t="s">
+      <c r="A226" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C226" s="3">
-        <v>0</v>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B227" s="2"/>
-      <c r="C227" s="2" t="s">
+      <c r="A227" s="3" t="s">
         <v>242</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C227" s="3">
+        <v>5034</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B228" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="C228" s="3">
-        <v>5035</v>
+        <v>4919</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="C229" s="3">
-        <v>4920</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C230" s="3">
-        <v>5395</v>
+        <v>5439</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
       <c r="C231" s="3">
-        <v>5440</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="C232" s="3">
-        <v>5230</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>245</v>
       </c>
       <c r="C233" s="3">
-        <v>5205</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>246</v>
       </c>
       <c r="C234" s="3">
-        <v>5040</v>
+        <v>5219</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="C235" s="3">
-        <v>5220</v>
+        <v>5624</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="C236" s="3">
-        <v>5625</v>
+        <v>5134</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="C237" s="3">
-        <v>5135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="C238" s="3">
         <v>0</v>
@@ -3722,7 +3719,7 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>248</v>
@@ -3733,23 +3730,12 @@
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>249</v>
       </c>
       <c r="C240" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C241" s="3">
         <v>0</v>
       </c>
     </row>

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2486.0</t>
+    <t>2476.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>11768.0</t>
+    <t>11628.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (20)</t>
   </si>
   <si>
-    <t>9767.0</t>
+    <t>9752.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -568,7 +568,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>166494.0</t>
+    <t>166294.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -1662,7 +1662,7 @@
         <v>61</v>
       </c>
       <c r="C50" s="3">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1759,7 +1759,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1411</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1803,7 +1803,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1789</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1814,7 +1814,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1339</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1964,7 +1964,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2433,7 +2433,7 @@
         <v>140</v>
       </c>
       <c r="C121" s="3">
-        <v>9600</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2840,7 +2840,7 @@
         <v>177</v>
       </c>
       <c r="C158" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -3256,7 +3256,7 @@
         <v>210</v>
       </c>
       <c r="C196" s="3">
-        <v>1872</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3498,7 +3498,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="3">
-        <v>1213</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="219" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -118,7 +118,7 @@
     <t>RELX Creator Pro Device (2)</t>
   </si>
   <si>
-    <t>12133.0</t>
+    <t>12118.0</t>
   </si>
   <si>
     <t>RELX Creator Pro Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>1385.0</t>
+    <t>1175.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>11628.0</t>
+    <t>11478.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (20)</t>
   </si>
   <si>
-    <t>9752.0</t>
+    <t>9732.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -361,7 +361,7 @@
     <t>RELX Pocket (G01BC) (6)</t>
   </si>
   <si>
-    <t>913.0</t>
+    <t>893.0</t>
   </si>
   <si>
     <t>RELX Pocket (G01BC)</t>
@@ -382,7 +382,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>43120.0</t>
+    <t>37470.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -568,7 +568,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>166294.0</t>
+    <t>159994.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -1435,7 +1435,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="3">
-        <v>6098</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1446,7 +1446,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <v>6035</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1477,7 +1477,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>184</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1565,7 +1565,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="3">
-        <v>165</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1609,7 +1609,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>1035</v>
+        <v>985</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1770,7 +1770,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2487</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1803,7 +1803,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1769</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1964,7 +1964,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -2182,7 +2182,7 @@
         <v>42</v>
       </c>
       <c r="C98" s="3">
-        <v>424</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2400,7 +2400,7 @@
         <v>137</v>
       </c>
       <c r="C118" s="3">
-        <v>2850</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -2433,7 +2433,7 @@
         <v>140</v>
       </c>
       <c r="C121" s="3">
-        <v>9500</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -2466,7 +2466,7 @@
         <v>143</v>
       </c>
       <c r="C124" s="3">
-        <v>7200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -2840,7 +2840,7 @@
         <v>177</v>
       </c>
       <c r="C158" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -2915,7 +2915,7 @@
         <v>186</v>
       </c>
       <c r="C165" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -2926,7 +2926,7 @@
         <v>144</v>
       </c>
       <c r="C166" s="3">
-        <v>3790</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -2948,7 +2948,7 @@
         <v>188</v>
       </c>
       <c r="C168" s="3">
-        <v>2154</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2959,7 +2959,7 @@
         <v>189</v>
       </c>
       <c r="C169" s="3">
-        <v>940</v>
+        <v>880</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -2992,7 +2992,7 @@
         <v>191</v>
       </c>
       <c r="C172" s="3">
-        <v>2610</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -3014,7 +3014,7 @@
         <v>83</v>
       </c>
       <c r="C174" s="3">
-        <v>4080</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3036,7 +3036,7 @@
         <v>194</v>
       </c>
       <c r="C176" s="3">
-        <v>760</v>
+        <v>560</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -3047,7 +3047,7 @@
         <v>195</v>
       </c>
       <c r="C177" s="3">
-        <v>5360</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3058,7 +3058,7 @@
         <v>196</v>
       </c>
       <c r="C178" s="3">
-        <v>3840</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3069,7 +3069,7 @@
         <v>197</v>
       </c>
       <c r="C179" s="3">
-        <v>6540</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3080,7 +3080,7 @@
         <v>198</v>
       </c>
       <c r="C180" s="3">
-        <v>510</v>
+        <v>460</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -3091,7 +3091,7 @@
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>5650</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3102,7 +3102,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>6185</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3124,7 +3124,7 @@
         <v>160</v>
       </c>
       <c r="C184" s="3">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3135,7 +3135,7 @@
         <v>202</v>
       </c>
       <c r="C185" s="3">
-        <v>2799</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3157,7 +3157,7 @@
         <v>204</v>
       </c>
       <c r="C187" s="3">
-        <v>839</v>
+        <v>639</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3168,7 +3168,7 @@
         <v>87</v>
       </c>
       <c r="C188" s="3">
-        <v>7519</v>
+        <v>6839</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3179,7 +3179,7 @@
         <v>205</v>
       </c>
       <c r="C189" s="3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3190,7 +3190,7 @@
         <v>206</v>
       </c>
       <c r="C190" s="3">
-        <v>1320</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3223,7 +3223,7 @@
         <v>140</v>
       </c>
       <c r="C193" s="3">
-        <v>1920</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3234,7 +3234,7 @@
         <v>208</v>
       </c>
       <c r="C194" s="3">
-        <v>9219</v>
+        <v>9069</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3245,7 +3245,7 @@
         <v>209</v>
       </c>
       <c r="C195" s="3">
-        <v>7979</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3256,7 +3256,7 @@
         <v>210</v>
       </c>
       <c r="C196" s="3">
-        <v>1722</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3267,7 +3267,7 @@
         <v>211</v>
       </c>
       <c r="C197" s="3">
-        <v>4700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -3278,7 +3278,7 @@
         <v>212</v>
       </c>
       <c r="C198" s="3">
-        <v>8870</v>
+        <v>8770</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -3311,7 +3311,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>11240</v>
+        <v>11150</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3322,7 +3322,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>5330</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3333,7 +3333,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>4880</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3355,7 +3355,7 @@
         <v>219</v>
       </c>
       <c r="C205" s="3">
-        <v>3900</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -3432,7 +3432,7 @@
         <v>53</v>
       </c>
       <c r="C212" s="3">
-        <v>2385</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -3454,7 +3454,7 @@
         <v>227</v>
       </c>
       <c r="C214" s="3">
-        <v>6919</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3465,7 +3465,7 @@
         <v>228</v>
       </c>
       <c r="C215" s="3">
-        <v>780</v>
+        <v>750</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -3476,7 +3476,7 @@
         <v>127</v>
       </c>
       <c r="C216" s="3">
-        <v>2560</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -3498,7 +3498,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="3">
-        <v>1163</v>
+        <v>213</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3520,7 +3520,7 @@
         <v>232</v>
       </c>
       <c r="C220" s="3">
-        <v>8175</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -3531,7 +3531,7 @@
         <v>233</v>
       </c>
       <c r="C221" s="3">
-        <v>8360</v>
+        <v>8330</v>
       </c>
     </row>
     <row r="222" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1704.0</t>
+    <t>1684.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -118,7 +118,7 @@
     <t>RELX Creator Pro Device (2)</t>
   </si>
   <si>
-    <t>12118.0</t>
+    <t>12081.0</t>
   </si>
   <si>
     <t>RELX Creator Pro Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>1175.0</t>
+    <t>1015.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2476.0</t>
+    <t>2319.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>11478.0</t>
+    <t>11179.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (20)</t>
   </si>
   <si>
-    <t>9732.0</t>
+    <t>9547.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -382,7 +382,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>37470.0</t>
+    <t>37460.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -568,7 +568,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>159994.0</t>
+    <t>151644.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -1327,7 +1327,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1704</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1435,7 +1435,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="3">
-        <v>6088</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1446,7 +1446,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <v>6030</v>
+        <v>6008</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1477,7 +1477,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>104</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1565,7 +1565,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="3">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1609,7 +1609,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>985</v>
+        <v>870</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1684,7 +1684,7 @@
         <v>63</v>
       </c>
       <c r="C52" s="3">
-        <v>794</v>
+        <v>784</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1706,7 +1706,7 @@
         <v>65</v>
       </c>
       <c r="C54" s="3">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1717,7 +1717,7 @@
         <v>66</v>
       </c>
       <c r="C55" s="3">
-        <v>1199</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1737,7 +1737,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2424</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>250</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1759,7 +1759,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1770,7 +1770,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2437</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1781,7 +1781,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>982</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1792,7 +1792,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>1036</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1814,7 +1814,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1319</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1964,7 +1964,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1975,7 +1975,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>1840</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1986,7 +1986,7 @@
         <v>97</v>
       </c>
       <c r="C80" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2019,7 +2019,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2118,7 +2118,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>1335</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2129,7 +2129,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>1665</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2162,7 +2162,7 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>1703</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2807,7 +2807,7 @@
         <v>174</v>
       </c>
       <c r="C155" s="3">
-        <v>2470</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2926,7 +2926,7 @@
         <v>144</v>
       </c>
       <c r="C166" s="3">
-        <v>3150</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -2948,7 +2948,7 @@
         <v>188</v>
       </c>
       <c r="C168" s="3">
-        <v>2114</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -2959,7 +2959,7 @@
         <v>189</v>
       </c>
       <c r="C169" s="3">
-        <v>880</v>
+        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -3014,7 +3014,7 @@
         <v>83</v>
       </c>
       <c r="C174" s="3">
-        <v>3830</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3036,7 +3036,7 @@
         <v>194</v>
       </c>
       <c r="C176" s="3">
-        <v>560</v>
+        <v>60</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -3047,7 +3047,7 @@
         <v>195</v>
       </c>
       <c r="C177" s="3">
-        <v>5040</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3058,7 +3058,7 @@
         <v>196</v>
       </c>
       <c r="C178" s="3">
-        <v>3720</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3069,7 +3069,7 @@
         <v>197</v>
       </c>
       <c r="C179" s="3">
-        <v>6440</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3080,7 +3080,7 @@
         <v>198</v>
       </c>
       <c r="C180" s="3">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -3091,7 +3091,7 @@
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>5330</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3113,7 +3113,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2566</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3124,7 +3124,7 @@
         <v>160</v>
       </c>
       <c r="C184" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3135,7 +3135,7 @@
         <v>202</v>
       </c>
       <c r="C185" s="3">
-        <v>2499</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3157,7 +3157,7 @@
         <v>204</v>
       </c>
       <c r="C187" s="3">
-        <v>639</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3168,7 +3168,7 @@
         <v>87</v>
       </c>
       <c r="C188" s="3">
-        <v>6839</v>
+        <v>6829</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3179,7 +3179,7 @@
         <v>205</v>
       </c>
       <c r="C189" s="3">
-        <v>2700</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3190,7 +3190,7 @@
         <v>206</v>
       </c>
       <c r="C190" s="3">
-        <v>1280</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3223,7 +3223,7 @@
         <v>140</v>
       </c>
       <c r="C193" s="3">
-        <v>1720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3234,7 +3234,7 @@
         <v>208</v>
       </c>
       <c r="C194" s="3">
-        <v>9069</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3256,7 +3256,7 @@
         <v>210</v>
       </c>
       <c r="C196" s="3">
-        <v>1562</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3311,7 +3311,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>11150</v>
+        <v>10950</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3333,7 +3333,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>4860</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3355,7 +3355,7 @@
         <v>219</v>
       </c>
       <c r="C205" s="3">
-        <v>3870</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -3432,7 +3432,7 @@
         <v>53</v>
       </c>
       <c r="C212" s="3">
-        <v>2185</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -3476,7 +3476,7 @@
         <v>127</v>
       </c>
       <c r="C216" s="3">
-        <v>2530</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -3498,7 +3498,7 @@
         <v>230</v>
       </c>
       <c r="C218" s="3">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="255">
   <si>
     <t>Name</t>
   </si>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>11179.0</t>
+    <t>11138.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -253,7 +253,7 @@
     <t>RELX MagicGo GA4000 (GA06B) (10)</t>
   </si>
   <si>
-    <t>5743.0</t>
+    <t>5793.0</t>
   </si>
   <si>
     <t>RELX MagicGo GA4000 (GA06B)</t>
@@ -289,10 +289,10 @@
     <t>Watermelon Chill|西瓜</t>
   </si>
   <si>
-    <t>RELX NOVA SILKMESH (20)</t>
-  </si>
-  <si>
-    <t>9547.0</t>
+    <t>RELX NOVA SILKMESH (25)</t>
+  </si>
+  <si>
+    <t>9512.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -304,9 +304,15 @@
     <t>Iced Cola</t>
   </si>
   <si>
+    <t>Coconut Water (New)</t>
+  </si>
+  <si>
     <t>Coconut Water</t>
   </si>
   <si>
+    <t>Grape Aloe</t>
+  </si>
+  <si>
     <t>Green Grape Ice</t>
   </si>
   <si>
@@ -325,6 +331,9 @@
     <t>Lychee Ice</t>
   </si>
   <si>
+    <t>Orange Soda</t>
+  </si>
+  <si>
     <t>Oolong Ice Tea</t>
   </si>
   <si>
@@ -340,6 +349,9 @@
     <t>Little Lime Pu-Erh Ice Tea</t>
   </si>
   <si>
+    <t>Rock Sugar Pear</t>
+  </si>
+  <si>
     <t>Sea Salt Lemon Ice</t>
   </si>
   <si>
@@ -349,6 +361,9 @@
     <t>Taro Scoop</t>
   </si>
   <si>
+    <t>Tangerine Splash</t>
+  </si>
+  <si>
     <t>White Pear Ice Tea</t>
   </si>
   <si>
@@ -382,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>37460.0</t>
+    <t>36260.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -568,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>151644.0</t>
+    <t>150934.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -748,22 +763,22 @@
     <t>Da Hong Pao Lemon Tea|大红袍</t>
   </si>
   <si>
+    <t>Hand Punch Lemon Ice Tea|维他柠檬茶</t>
+  </si>
+  <si>
     <t>Mango Ice Tea|芒果绿茶</t>
   </si>
   <si>
+    <t>Pineapple Lemon|柠檬菠萝</t>
+  </si>
+  <si>
+    <t>Passion Fruit Ice|百香果</t>
+  </si>
+  <si>
     <t>Fresh Strawberry|草莓</t>
   </si>
   <si>
     <t>Red Wine Ice|红酒冰</t>
-  </si>
-  <si>
-    <t>Hand Punch Lemon Ice Tea|维他柠檬茶</t>
-  </si>
-  <si>
-    <t>Passion Fruit Ice|百香果</t>
-  </si>
-  <si>
-    <t>Pineapple Lemon|柠檬菠萝</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C240"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="30.7109375" customWidth="1"/>
@@ -1748,7 +1763,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1759,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1310</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1792,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>1021</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1803,7 +1818,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1719</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1834,7 +1849,7 @@
         <v>81</v>
       </c>
       <c r="C66" s="3">
-        <v>866</v>
+        <v>876</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1845,7 +1860,7 @@
         <v>82</v>
       </c>
       <c r="C67" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1867,7 +1882,7 @@
         <v>84</v>
       </c>
       <c r="C69" s="3">
-        <v>1036</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1911,7 +1926,7 @@
         <v>88</v>
       </c>
       <c r="C73" s="3">
-        <v>1447</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1933,7 +1948,7 @@
         <v>90</v>
       </c>
       <c r="C75" s="3">
-        <v>650</v>
+        <v>660</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1975,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>1835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1986,7 +2001,7 @@
         <v>97</v>
       </c>
       <c r="C80" s="3">
-        <v>0</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2008,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>590</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2019,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2030,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>0</v>
+        <v>585</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2041,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2074,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2085,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2096,7 +2111,7 @@
         <v>107</v>
       </c>
       <c r="C90" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2107,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>540</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2118,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>1230</v>
+        <v>820</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2129,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>1660</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2151,7 +2166,7 @@
         <v>112</v>
       </c>
       <c r="C95" s="3">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2162,43 +2177,45 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>1673</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2" t="s">
-        <v>115</v>
+      <c r="C97" s="3">
+        <v>1660</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="C99" s="3">
-        <v>489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>117</v>
@@ -2209,52 +2226,52 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="3" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>0</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B102" s="3" t="s">
+      <c r="A102" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C102" s="3">
-        <v>0</v>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="C103" s="3">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2" t="s">
-        <v>122</v>
+      <c r="B104" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" s="3">
+        <v>489</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C105" s="3">
         <v>0</v>
@@ -2262,10 +2279,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="C106" s="3">
         <v>0</v>
@@ -2273,10 +2290,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C107" s="3">
         <v>0</v>
@@ -2284,29 +2301,27 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C108" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C109" s="3">
-        <v>2090</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>129</v>
@@ -2317,7 +2332,7 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>130</v>
@@ -2328,7 +2343,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>131</v>
@@ -2339,7 +2354,7 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>132</v>
@@ -2350,29 +2365,29 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C114" s="3">
-        <v>0</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>134</v>
       </c>
       <c r="C115" s="3">
-        <v>1890</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>135</v>
@@ -2383,7 +2398,7 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>136</v>
@@ -2394,18 +2409,18 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C118" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>138</v>
@@ -2416,29 +2431,29 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C120" s="3">
-        <v>0</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C121" s="3">
-        <v>7100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>141</v>
@@ -2449,29 +2464,29 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C123" s="3">
-        <v>3250</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>143</v>
       </c>
       <c r="C124" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>144</v>
@@ -2482,18 +2497,18 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>145</v>
       </c>
       <c r="C126" s="3">
-        <v>0</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>146</v>
@@ -2504,29 +2519,29 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C128" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C129" s="3">
-        <v>200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>149</v>
@@ -2537,7 +2552,7 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>150</v>
@@ -2548,7 +2563,7 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>151</v>
@@ -2559,7 +2574,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>152</v>
@@ -2570,18 +2585,18 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>153</v>
       </c>
       <c r="C134" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>154</v>
@@ -2592,7 +2607,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>155</v>
@@ -2603,7 +2618,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>156</v>
@@ -2614,7 +2629,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>157</v>
@@ -2625,18 +2640,18 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>158</v>
       </c>
       <c r="C139" s="3">
-        <v>5700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>159</v>
@@ -2647,18 +2662,18 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C141" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>161</v>
@@ -2669,7 +2684,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>162</v>
@@ -2680,40 +2695,40 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C144" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>164</v>
       </c>
       <c r="C145" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>165</v>
       </c>
       <c r="C146" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>166</v>
@@ -2724,7 +2739,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>167</v>
@@ -2735,7 +2750,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>168</v>
@@ -2746,18 +2761,18 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>169</v>
       </c>
       <c r="C150" s="3">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>170</v>
@@ -2768,7 +2783,7 @@
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>171</v>
@@ -2779,7 +2794,7 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>172</v>
@@ -2790,7 +2805,7 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>173</v>
@@ -2801,18 +2816,18 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>174</v>
       </c>
       <c r="C155" s="3">
-        <v>2460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>175</v>
@@ -2823,7 +2838,7 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>176</v>
@@ -2834,7 +2849,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>177</v>
@@ -2845,7 +2860,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>178</v>
@@ -2856,18 +2871,18 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C160" s="3">
-        <v>0</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>180</v>
@@ -2878,18 +2893,18 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C162" s="3">
-        <v>6720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>182</v>
@@ -2899,20 +2914,22 @@
       </c>
     </row>
     <row r="164" spans="1:3">
-      <c r="A164" s="2" t="s">
+      <c r="A164" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B164" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2" t="s">
-        <v>184</v>
+      <c r="C164" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165" s="3" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C165" s="3">
         <v>0</v>
@@ -2920,54 +2937,52 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B166" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C166" s="3">
-        <v>2390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="3" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C167" s="3">
-        <v>0</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168" s="3" t="s">
-        <v>185</v>
+        <v>128</v>
       </c>
       <c r="B168" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C168" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C168" s="3">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2"/>
+      <c r="C169" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C169" s="3">
-        <v>270</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>43</v>
+        <v>191</v>
       </c>
       <c r="C170" s="3">
         <v>0</v>
@@ -2975,54 +2990,54 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>0</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C172" s="3">
-        <v>2580</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C173" s="3">
-        <v>0</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>83</v>
+        <v>194</v>
       </c>
       <c r="C174" s="3">
-        <v>2800</v>
+        <v>260</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="C175" s="3">
         <v>0</v>
@@ -3030,175 +3045,175 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C176" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C177" s="3">
-        <v>4940</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C178" s="3">
-        <v>3070</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>6190</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>198</v>
       </c>
       <c r="C180" s="3">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>5300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>6135</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2466</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>0</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C185" s="3">
-        <v>2079</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>0</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>439</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>6829</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C189" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>1080</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C191" s="3">
         <v>0</v>
@@ -3206,512 +3221,512 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="C192" s="3">
-        <v>0</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>700</v>
+        <v>6709</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C194" s="3">
-        <v>8669</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>7939</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C196" s="3">
-        <v>1502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="C197" s="3">
-        <v>4400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="C198" s="3">
-        <v>8770</v>
+        <v>700</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C199" s="3">
-        <v>570</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C200" s="3">
-        <v>0</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>10950</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>5230</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>4890</v>
+        <v>8750</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>218</v>
       </c>
       <c r="C204" s="3">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C205" s="3">
-        <v>3840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B206" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>400</v>
+        <v>10940</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>221</v>
       </c>
       <c r="C207" s="3">
-        <v>0</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C208" s="3">
-        <v>516</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>223</v>
       </c>
       <c r="C209" s="3">
-        <v>819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>0</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="C212" s="3">
-        <v>1735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C213" s="3">
-        <v>3615</v>
+        <v>496</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>6889</v>
+        <v>799</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C215" s="3">
-        <v>750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="C216" s="3">
-        <v>2020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>0</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C218" s="3">
-        <v>13</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C219" s="3">
-        <v>9780</v>
+        <v>6889</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C220" s="3">
-        <v>8035</v>
+        <v>750</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>233</v>
+        <v>132</v>
       </c>
       <c r="C221" s="3">
-        <v>8330</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="2" t="s">
+      <c r="A222" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B222" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2" t="s">
-        <v>235</v>
+      <c r="C222" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="3" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C223" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B224" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="C224" s="3">
-        <v>0</v>
+        <v>9770</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225" s="3" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="B225" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C225" s="3">
+        <v>8035</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C226" s="3">
+        <v>8330</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C225" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="2" t="s">
+      <c r="B227" s="2"/>
+      <c r="C227" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="B226" s="2"/>
-      <c r="C226" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
-      <c r="A227" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C227" s="3">
-        <v>5034</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B228" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B228" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="C228" s="3">
-        <v>4919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>49</v>
+        <v>243</v>
       </c>
       <c r="C229" s="3">
-        <v>5394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>44</v>
+        <v>244</v>
       </c>
       <c r="C230" s="3">
-        <v>5439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C231" s="3">
-        <v>5229</v>
+      <c r="A231" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>244</v>
+        <v>41</v>
       </c>
       <c r="C232" s="3">
-        <v>5204</v>
+        <v>5034</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="C233" s="3">
-        <v>5039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C234" s="3">
-        <v>5219</v>
+        <v>4919</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C235" s="3">
-        <v>5624</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="C236" s="3">
-        <v>5134</v>
+        <v>5439</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="C237" s="3">
-        <v>0</v>
+        <v>5229</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C238" s="3">
         <v>0</v>
@@ -3719,24 +3734,79 @@
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C239" s="3">
-        <v>0</v>
+        <v>5204</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C240" s="3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C241" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C242" s="3">
+        <v>5039</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C243" s="3">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C244" s="3">
+        <v>5624</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C245" s="3">
+        <v>5134</v>
       </c>
     </row>
   </sheetData>

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1684.0</t>
+    <t>1674.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>9512.0</t>
+    <t>9477.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1684</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2133,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>820</v>
+        <v>795</v>
       </c>
     </row>
     <row r="93" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1674.0</t>
+    <t>1664.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -118,7 +118,7 @@
     <t>RELX Creator Pro Device (2)</t>
   </si>
   <si>
-    <t>12081.0</t>
+    <t>12059.0</t>
   </si>
   <si>
     <t>RELX Creator Pro Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>1015.0</t>
+    <t>925.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2319.0</t>
+    <t>2289.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>11138.0</t>
+    <t>10882.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -253,7 +253,7 @@
     <t>RELX MagicGo GA4000 (GA06B) (10)</t>
   </si>
   <si>
-    <t>5793.0</t>
+    <t>5743.0</t>
   </si>
   <si>
     <t>RELX MagicGo GA4000 (GA06B)</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>9477.0</t>
+    <t>47757.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -376,7 +376,7 @@
     <t>RELX Pocket (G01BC) (6)</t>
   </si>
   <si>
-    <t>893.0</t>
+    <t>888.0</t>
   </si>
   <si>
     <t>RELX Pocket (G01BC)</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>36260.0</t>
+    <t>36150.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>150934.0</t>
+    <t>146744.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -754,7 +754,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>52235.0</t>
+    <t>52025.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1674</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1450,7 +1450,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="3">
-        <v>6073</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1461,7 +1461,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <v>6008</v>
+        <v>5997</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1492,7 +1492,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1580,7 +1580,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="3">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1624,7 +1624,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>870</v>
+        <v>840</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1699,7 +1699,7 @@
         <v>63</v>
       </c>
       <c r="C52" s="3">
-        <v>784</v>
+        <v>774</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1732,7 +1732,7 @@
         <v>66</v>
       </c>
       <c r="C55" s="3">
-        <v>1054</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2261</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1763,7 +1763,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1774,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2417</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>1002</v>
+        <v>972</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1807,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>1010</v>
+        <v>970</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1709</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1309</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1926,7 +1926,7 @@
         <v>88</v>
       </c>
       <c r="C73" s="3">
-        <v>1457</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1968,7 +1968,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>105</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1979,7 +1979,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>0</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1990,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>0</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2001,7 +2001,7 @@
         <v>97</v>
       </c>
       <c r="C80" s="3">
-        <v>1835</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>0</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2023,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>0</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2034,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>575</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>5</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2067,7 +2067,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>0</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2078,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>0</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>0</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>0</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2111,7 +2111,7 @@
         <v>107</v>
       </c>
       <c r="C90" s="3">
-        <v>0</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2122,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>1054</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2133,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>795</v>
+        <v>440</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2144,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>5</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>0</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2166,7 +2166,7 @@
         <v>112</v>
       </c>
       <c r="C95" s="3">
-        <v>540</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2177,7 +2177,7 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>1230</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2188,7 +2188,7 @@
         <v>114</v>
       </c>
       <c r="C97" s="3">
-        <v>1660</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>0</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2210,7 +2210,7 @@
         <v>116</v>
       </c>
       <c r="C99" s="3">
-        <v>0</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2221,7 +2221,7 @@
         <v>117</v>
       </c>
       <c r="C100" s="3">
-        <v>0</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2232,7 +2232,7 @@
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>1673</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2252,7 +2252,7 @@
         <v>42</v>
       </c>
       <c r="C103" s="3">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -2503,7 +2503,7 @@
         <v>145</v>
       </c>
       <c r="C126" s="3">
-        <v>6550</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2525,7 +2525,7 @@
         <v>147</v>
       </c>
       <c r="C128" s="3">
-        <v>3200</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -2996,7 +2996,7 @@
         <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>2390</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3018,7 +3018,7 @@
         <v>193</v>
       </c>
       <c r="C173" s="3">
-        <v>2104</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -3029,7 +3029,7 @@
         <v>194</v>
       </c>
       <c r="C174" s="3">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3062,7 +3062,7 @@
         <v>196</v>
       </c>
       <c r="C177" s="3">
-        <v>2570</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3084,7 +3084,7 @@
         <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>2790</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3106,7 +3106,7 @@
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3117,7 +3117,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>4940</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3128,7 +3128,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>3040</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3139,7 +3139,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>6190</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3150,7 +3150,7 @@
         <v>203</v>
       </c>
       <c r="C185" s="3">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>5270</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3172,7 +3172,7 @@
         <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>6135</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3183,7 +3183,7 @@
         <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>2446</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>1939</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3227,7 +3227,7 @@
         <v>209</v>
       </c>
       <c r="C192" s="3">
-        <v>429</v>
+        <v>359</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>6709</v>
+        <v>6539</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3249,7 +3249,7 @@
         <v>210</v>
       </c>
       <c r="C194" s="3">
-        <v>2090</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3260,7 +3260,7 @@
         <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>1050</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3293,7 +3293,7 @@
         <v>145</v>
       </c>
       <c r="C198" s="3">
-        <v>700</v>
+        <v>580</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -3304,7 +3304,7 @@
         <v>213</v>
       </c>
       <c r="C199" s="3">
-        <v>8669</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -3315,7 +3315,7 @@
         <v>214</v>
       </c>
       <c r="C200" s="3">
-        <v>7919</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -3326,7 +3326,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>1472</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3337,7 +3337,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>4350</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3348,7 +3348,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>8750</v>
+        <v>8680</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3359,7 +3359,7 @@
         <v>218</v>
       </c>
       <c r="C204" s="3">
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -3381,7 +3381,7 @@
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>10940</v>
+        <v>10660</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3392,7 +3392,7 @@
         <v>221</v>
       </c>
       <c r="C207" s="3">
-        <v>5230</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -3403,7 +3403,7 @@
         <v>222</v>
       </c>
       <c r="C208" s="3">
-        <v>4890</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -3425,7 +3425,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>3840</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3436,7 +3436,7 @@
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -3458,7 +3458,7 @@
         <v>227</v>
       </c>
       <c r="C213" s="3">
-        <v>496</v>
+        <v>266</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -3469,7 +3469,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>799</v>
+        <v>779</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3502,7 +3502,7 @@
         <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>1705</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3524,7 +3524,7 @@
         <v>232</v>
       </c>
       <c r="C219" s="3">
-        <v>6889</v>
+        <v>6869</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -3535,7 +3535,7 @@
         <v>233</v>
       </c>
       <c r="C220" s="3">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -3546,7 +3546,7 @@
         <v>132</v>
       </c>
       <c r="C221" s="3">
-        <v>2010</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -3579,7 +3579,7 @@
         <v>236</v>
       </c>
       <c r="C224" s="3">
-        <v>9770</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -3590,7 +3590,7 @@
         <v>237</v>
       </c>
       <c r="C225" s="3">
-        <v>8035</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -3601,7 +3601,7 @@
         <v>238</v>
       </c>
       <c r="C226" s="3">
-        <v>8330</v>
+        <v>8310</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -3663,7 +3663,7 @@
         <v>41</v>
       </c>
       <c r="C232" s="3">
-        <v>5034</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -3685,7 +3685,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="3">
-        <v>4919</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3696,7 +3696,7 @@
         <v>49</v>
       </c>
       <c r="C235" s="3">
-        <v>5394</v>
+        <v>5324</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -3718,7 +3718,7 @@
         <v>196</v>
       </c>
       <c r="C237" s="3">
-        <v>5229</v>
+        <v>5209</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3740,7 +3740,7 @@
         <v>250</v>
       </c>
       <c r="C239" s="3">
-        <v>5204</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3773,7 +3773,7 @@
         <v>253</v>
       </c>
       <c r="C242" s="3">
-        <v>5039</v>
+        <v>5019</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3795,7 +3795,7 @@
         <v>56</v>
       </c>
       <c r="C244" s="3">
-        <v>5624</v>
+        <v>5604</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -3806,7 +3806,7 @@
         <v>125</v>
       </c>
       <c r="C245" s="3">
-        <v>5134</v>
+        <v>5114</v>
       </c>
     </row>
   </sheetData>

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -28,7 +28,7 @@
     <t>Bubblemon (15)</t>
   </si>
   <si>
-    <t>807.0</t>
+    <t>805.0</t>
   </si>
   <si>
     <t>Bubblemon</t>
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2289.0</t>
+    <t>2269.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10882.0</t>
+    <t>10826.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>47757.0</t>
+    <t>46302.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>36150.0</t>
+    <t>35850.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>146744.0</t>
+    <t>144794.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -754,7 +754,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>52025.0</t>
+    <t>51575.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="3">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1699,7 +1699,7 @@
         <v>63</v>
       </c>
       <c r="C52" s="3">
-        <v>774</v>
+        <v>754</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2235</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2377</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>972</v>
+        <v>962</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1807,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>970</v>
+        <v>965</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1269</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1968,7 +1968,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>2405</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1979,7 +1979,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>1770</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1990,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>2385</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>1560</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2023,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>1475</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2034,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>2100</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>4100</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>1735</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2067,7 +2067,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>2005</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2078,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>1145</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1655</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2520</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2111,7 +2111,7 @@
         <v>107</v>
       </c>
       <c r="C90" s="3">
-        <v>1045</v>
+        <v>970</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2122,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>2819</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2133,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1590</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2166,7 +2166,7 @@
         <v>112</v>
       </c>
       <c r="C95" s="3">
-        <v>2285</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2177,7 +2177,7 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>1005</v>
+        <v>960</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2188,7 +2188,7 @@
         <v>114</v>
       </c>
       <c r="C97" s="3">
-        <v>1300</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1640</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2210,7 +2210,7 @@
         <v>116</v>
       </c>
       <c r="C99" s="3">
-        <v>1305</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2221,7 +2221,7 @@
         <v>117</v>
       </c>
       <c r="C100" s="3">
-        <v>1730</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2232,7 +2232,7 @@
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>3228</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2470,7 +2470,7 @@
         <v>142</v>
       </c>
       <c r="C123" s="3">
-        <v>400</v>
+        <v>320</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2503,7 +2503,7 @@
         <v>145</v>
       </c>
       <c r="C126" s="3">
-        <v>6450</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2536,7 +2536,7 @@
         <v>148</v>
       </c>
       <c r="C129" s="3">
-        <v>6000</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2723,7 +2723,7 @@
         <v>165</v>
       </c>
       <c r="C146" s="3">
-        <v>800</v>
+        <v>720</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -2767,7 +2767,7 @@
         <v>169</v>
       </c>
       <c r="C150" s="3">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -2954,7 +2954,7 @@
         <v>186</v>
       </c>
       <c r="C167" s="3">
-        <v>6720</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -2996,7 +2996,7 @@
         <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>2220</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3062,7 +3062,7 @@
         <v>196</v>
       </c>
       <c r="C177" s="3">
-        <v>2550</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3084,7 +3084,7 @@
         <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>2690</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3106,7 +3106,7 @@
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3117,7 +3117,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>4860</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3128,7 +3128,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2780</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3139,7 +3139,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>6140</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3150,7 +3150,7 @@
         <v>203</v>
       </c>
       <c r="C185" s="3">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>4950</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3172,7 +3172,7 @@
         <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>6105</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>1719</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3227,7 +3227,7 @@
         <v>209</v>
       </c>
       <c r="C192" s="3">
-        <v>359</v>
+        <v>559</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>6539</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3304,7 +3304,7 @@
         <v>213</v>
       </c>
       <c r="C199" s="3">
-        <v>8519</v>
+        <v>8509</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -3326,7 +3326,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>1372</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3337,7 +3337,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>4300</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3359,7 +3359,7 @@
         <v>218</v>
       </c>
       <c r="C204" s="3">
-        <v>550</v>
+        <v>520</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -3381,7 +3381,7 @@
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>10660</v>
+        <v>10710</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3425,7 +3425,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>3790</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3436,7 +3436,7 @@
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -3469,7 +3469,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>779</v>
+        <v>569</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3502,7 +3502,7 @@
         <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>1425</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3513,7 +3513,7 @@
         <v>231</v>
       </c>
       <c r="C218" s="3">
-        <v>3605</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3524,7 +3524,7 @@
         <v>232</v>
       </c>
       <c r="C219" s="3">
-        <v>6869</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -3685,7 +3685,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="3">
-        <v>4899</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3696,7 +3696,7 @@
         <v>49</v>
       </c>
       <c r="C235" s="3">
-        <v>5324</v>
+        <v>5264</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -3707,7 +3707,7 @@
         <v>44</v>
       </c>
       <c r="C236" s="3">
-        <v>5439</v>
+        <v>5409</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -3718,7 +3718,7 @@
         <v>196</v>
       </c>
       <c r="C237" s="3">
-        <v>5209</v>
+        <v>5149</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3740,7 +3740,7 @@
         <v>250</v>
       </c>
       <c r="C239" s="3">
-        <v>5184</v>
+        <v>5124</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -3773,7 +3773,7 @@
         <v>253</v>
       </c>
       <c r="C242" s="3">
-        <v>5019</v>
+        <v>4989</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3784,7 +3784,7 @@
         <v>254</v>
       </c>
       <c r="C243" s="3">
-        <v>5219</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -3795,7 +3795,7 @@
         <v>56</v>
       </c>
       <c r="C244" s="3">
-        <v>5604</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -3806,7 +3806,7 @@
         <v>125</v>
       </c>
       <c r="C245" s="3">
-        <v>5114</v>
+        <v>5054</v>
       </c>
     </row>
   </sheetData>

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1664.0</t>
+    <t>1614.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -118,7 +118,7 @@
     <t>RELX Creator Pro Device (2)</t>
   </si>
   <si>
-    <t>12059.0</t>
+    <t>12044.0</t>
   </si>
   <si>
     <t>RELX Creator Pro Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>925.0</t>
+    <t>850.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10826.0</t>
+    <t>10706.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -253,7 +253,7 @@
     <t>RELX MagicGo GA4000 (GA06B) (10)</t>
   </si>
   <si>
-    <t>5743.0</t>
+    <t>5738.0</t>
   </si>
   <si>
     <t>RELX MagicGo GA4000 (GA06B)</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>46302.0</t>
+    <t>45317.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>144794.0</t>
+    <t>142924.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -754,7 +754,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>51575.0</t>
+    <t>51555.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1664</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1450,7 +1450,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="3">
-        <v>6062</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1461,7 +1461,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="3">
-        <v>5997</v>
+        <v>5987</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1492,7 +1492,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1580,7 +1580,7 @@
         <v>50</v>
       </c>
       <c r="C41" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1624,7 +1624,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>840</v>
+        <v>820</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2215</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1774,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1290</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2367</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>962</v>
+        <v>862</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1669</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1860,7 +1860,7 @@
         <v>82</v>
       </c>
       <c r="C67" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1968,7 +1968,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>2390</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1979,7 +1979,7 @@
         <v>95</v>
       </c>
       <c r="C78" s="3">
-        <v>1740</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1990,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>2345</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2001,7 +2001,7 @@
         <v>97</v>
       </c>
       <c r="C80" s="3">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>1455</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2023,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>1360</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2034,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>2040</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>4055</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>1725</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2067,7 +2067,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>1935</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2078,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>1085</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1520</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2405</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2122,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>2799</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2133,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>410</v>
+        <v>394</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2144,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>2690</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1515</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2166,7 +2166,7 @@
         <v>112</v>
       </c>
       <c r="C95" s="3">
-        <v>2250</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -2177,7 +2177,7 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>960</v>
+        <v>945</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2188,7 +2188,7 @@
         <v>114</v>
       </c>
       <c r="C97" s="3">
-        <v>1255</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1520</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2210,7 +2210,7 @@
         <v>116</v>
       </c>
       <c r="C99" s="3">
-        <v>1220</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2221,7 +2221,7 @@
         <v>117</v>
       </c>
       <c r="C100" s="3">
-        <v>1650</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2232,7 +2232,7 @@
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>3183</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3084,7 +3084,7 @@
         <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>2680</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3106,7 +3106,7 @@
         <v>199</v>
       </c>
       <c r="C181" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -3139,7 +3139,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>6110</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>3620</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3172,7 +3172,7 @@
         <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>6155</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3183,7 +3183,7 @@
         <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>2226</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>6319</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3260,7 +3260,7 @@
         <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>1030</v>
+        <v>930</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3326,7 +3326,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>1272</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3348,7 +3348,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>8680</v>
+        <v>8630</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3425,7 +3425,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>3740</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3663,7 +3663,7 @@
         <v>41</v>
       </c>
       <c r="C232" s="3">
-        <v>5014</v>
+        <v>5009</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -3685,7 +3685,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="3">
-        <v>4839</v>
+        <v>4834</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3707,7 +3707,7 @@
         <v>44</v>
       </c>
       <c r="C236" s="3">
-        <v>5409</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -3740,7 +3740,7 @@
         <v>250</v>
       </c>
       <c r="C239" s="3">
-        <v>5124</v>
+        <v>5119</v>
       </c>
     </row>
     <row r="240" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>45317.0</t>
+    <t>44997.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>35850.0</t>
+    <t>35650.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -1990,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>2340</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>1015</v>
+        <v>965</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2034,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>1970</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>4010</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>1710</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2067,7 +2067,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>1910</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2078,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>1075</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1474</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2365</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2111,7 +2111,7 @@
         <v>107</v>
       </c>
       <c r="C90" s="3">
-        <v>970</v>
+        <v>950</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2133,7 +2133,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2144,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>2665</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1480</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1485</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2210,7 +2210,7 @@
         <v>116</v>
       </c>
       <c r="C99" s="3">
-        <v>1215</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2503,7 +2503,7 @@
         <v>145</v>
       </c>
       <c r="C126" s="3">
-        <v>6440</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="127" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>850.0</t>
+    <t>810.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10706.0</t>
+    <t>10661.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -253,7 +253,7 @@
     <t>RELX MagicGo GA4000 (GA06B) (10)</t>
   </si>
   <si>
-    <t>5738.0</t>
+    <t>5718.0</t>
   </si>
   <si>
     <t>RELX MagicGo GA4000 (GA06B)</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>44997.0</t>
+    <t>44617.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -376,7 +376,7 @@
     <t>RELX Pocket (G01BC) (6)</t>
   </si>
   <si>
-    <t>888.0</t>
+    <t>883.0</t>
   </si>
   <si>
     <t>RELX Pocket (G01BC)</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>142924.0</t>
+    <t>142104.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -1492,7 +1492,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="3">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1624,7 +1624,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>820</v>
+        <v>795</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2210</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1763,7 +1763,7 @@
         <v>71</v>
       </c>
       <c r="C58" s="3">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2362</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>74</v>
       </c>
       <c r="C61" s="3">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1664</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1893,7 +1893,7 @@
         <v>85</v>
       </c>
       <c r="C70" s="3">
-        <v>1103</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1968,7 +1968,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>2365</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1990,7 +1990,7 @@
         <v>96</v>
       </c>
       <c r="C79" s="3">
-        <v>2320</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>965</v>
+        <v>935</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2023,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>1325</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>3990</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>1690</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1444</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2111,7 +2111,7 @@
         <v>107</v>
       </c>
       <c r="C90" s="3">
-        <v>950</v>
+        <v>920</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -2122,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>2769</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2144,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>2655</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1460</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2177,7 +2177,7 @@
         <v>113</v>
       </c>
       <c r="C96" s="3">
-        <v>945</v>
+        <v>910</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1455</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2210,7 +2210,7 @@
         <v>116</v>
       </c>
       <c r="C99" s="3">
-        <v>1195</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -2232,7 +2232,7 @@
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>3157</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2263,7 +2263,7 @@
         <v>41</v>
       </c>
       <c r="C104" s="3">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -3018,7 +3018,7 @@
         <v>193</v>
       </c>
       <c r="C173" s="3">
-        <v>1814</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -3084,7 +3084,7 @@
         <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>2480</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3117,7 +3117,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>4950</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3139,7 +3139,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>6010</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3183,7 +3183,7 @@
         <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>2026</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>1149</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>5919</v>
+        <v>5849</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3249,7 +3249,7 @@
         <v>210</v>
       </c>
       <c r="C194" s="3">
-        <v>2040</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3260,7 +3260,7 @@
         <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>930</v>
+        <v>920</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3315,7 +3315,7 @@
         <v>214</v>
       </c>
       <c r="C200" s="3">
-        <v>7899</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -3326,7 +3326,7 @@
         <v>215</v>
       </c>
       <c r="C201" s="3">
-        <v>1052</v>
+        <v>972</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3337,7 +3337,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>4350</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3348,7 +3348,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>8630</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3381,7 +3381,7 @@
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>10710</v>
+        <v>10670</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3436,7 +3436,7 @@
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>210</v>
+        <v>180</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -3469,7 +3469,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>569</v>
+        <v>549</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3502,7 +3502,7 @@
         <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>1525</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3513,7 +3513,7 @@
         <v>231</v>
       </c>
       <c r="C218" s="3">
-        <v>3595</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3546,7 +3546,7 @@
         <v>132</v>
       </c>
       <c r="C221" s="3">
-        <v>1990</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -3590,7 +3590,7 @@
         <v>237</v>
       </c>
       <c r="C225" s="3">
-        <v>7975</v>
+        <v>7895</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -3601,7 +3601,7 @@
         <v>238</v>
       </c>
       <c r="C226" s="3">
-        <v>8310</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="227" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1614.0</t>
+    <t>1599.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -133,7 +133,7 @@
     <t>RELX Creator SilkMesh Pod (16)</t>
   </si>
   <si>
-    <t>810.0</t>
+    <t>740.0</t>
   </si>
   <si>
     <t>RELX Creator SilkMesh Pod</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10661.0</t>
+    <t>10616.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>44617.0</t>
+    <t>44507.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>35650.0</t>
+    <t>35450.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>142104.0</t>
+    <t>140734.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1614</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1624,7 +1624,7 @@
         <v>54</v>
       </c>
       <c r="C45" s="3">
-        <v>795</v>
+        <v>725</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2195</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2357</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1258</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>935</v>
+        <v>920</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2023,7 +2023,7 @@
         <v>99</v>
       </c>
       <c r="C82" s="3">
-        <v>1300</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -2034,7 +2034,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>1965</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2045,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>3985</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1424</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2345</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1440</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1435</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2470,7 +2470,7 @@
         <v>142</v>
       </c>
       <c r="C123" s="3">
-        <v>320</v>
+        <v>120</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -2996,7 +2996,7 @@
         <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>2420</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3084,7 +3084,7 @@
         <v>83</v>
       </c>
       <c r="C179" s="3">
-        <v>2450</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3117,7 +3117,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>4940</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3128,7 +3128,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2730</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>3420</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>1049</v>
+        <v>849</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>5849</v>
+        <v>5449</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3260,7 +3260,7 @@
         <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>920</v>
+        <v>910</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3293,7 +3293,7 @@
         <v>145</v>
       </c>
       <c r="C198" s="3">
-        <v>580</v>
+        <v>560</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -3315,7 +3315,7 @@
         <v>214</v>
       </c>
       <c r="C200" s="3">
-        <v>7879</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -3337,7 +3337,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>4310</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3425,7 +3425,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>3640</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3469,7 +3469,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>549</v>
+        <v>529</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3502,7 +3502,7 @@
         <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>1505</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3546,7 +3546,7 @@
         <v>132</v>
       </c>
       <c r="C221" s="3">
-        <v>1960</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="222" spans="1:3">

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -82,7 +82,7 @@
     <t>RELX Artisan Device (9)</t>
   </si>
   <si>
-    <t>1599.0</t>
+    <t>1583.0</t>
   </si>
   <si>
     <t>RELX Artisan Device</t>
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2269.0</t>
+    <t>2264.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10616.0</t>
+    <t>10409.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>44507.0</t>
+    <t>44422.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>35450.0</t>
+    <t>34750.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -583,7 +583,7 @@
     <t>RELX Pod Pro 2-3 Pods (57)</t>
   </si>
   <si>
-    <t>140734.0</t>
+    <t>139314.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -754,7 +754,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>51555.0</t>
+    <t>51505.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1342,7 +1342,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3">
-        <v>1599</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1732,7 +1732,7 @@
         <v>66</v>
       </c>
       <c r="C55" s="3">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1752,7 +1752,7 @@
         <v>70</v>
       </c>
       <c r="C57" s="3">
-        <v>2185</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1774,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1285</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1785,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="C60" s="3">
-        <v>2342</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1807,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>965</v>
+        <v>945</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="3">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="3">
-        <v>1238</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1968,7 +1968,7 @@
         <v>94</v>
       </c>
       <c r="C77" s="3">
-        <v>2360</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -2012,7 +2012,7 @@
         <v>98</v>
       </c>
       <c r="C81" s="3">
-        <v>920</v>
+        <v>910</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -2056,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="C85" s="3">
-        <v>1660</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -2067,7 +2067,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>1890</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2078,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2089,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1409</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2100,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2335</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2122,7 +2122,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>2754</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2144,7 +2144,7 @@
         <v>110</v>
       </c>
       <c r="C93" s="3">
-        <v>2640</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2155,7 +2155,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1425</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2188,7 +2188,7 @@
         <v>114</v>
       </c>
       <c r="C97" s="3">
-        <v>1239</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -2199,7 +2199,7 @@
         <v>115</v>
       </c>
       <c r="C98" s="3">
-        <v>1420</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -2371,7 +2371,7 @@
         <v>133</v>
       </c>
       <c r="C114" s="3">
-        <v>2090</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -2536,7 +2536,7 @@
         <v>148</v>
       </c>
       <c r="C129" s="3">
-        <v>5980</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -2996,7 +2996,7 @@
         <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>2410</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3018,7 +3018,7 @@
         <v>193</v>
       </c>
       <c r="C173" s="3">
-        <v>1794</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -3029,7 +3029,7 @@
         <v>194</v>
       </c>
       <c r="C174" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3062,7 +3062,7 @@
         <v>196</v>
       </c>
       <c r="C177" s="3">
-        <v>2490</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3117,7 +3117,7 @@
         <v>200</v>
       </c>
       <c r="C182" s="3">
-        <v>4930</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3128,7 +3128,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2680</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3139,7 +3139,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>5990</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3150,7 +3150,7 @@
         <v>203</v>
       </c>
       <c r="C185" s="3">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3161,7 +3161,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>3400</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3172,7 +3172,7 @@
         <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>6055</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3183,7 +3183,7 @@
         <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>1996</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>207</v>
       </c>
       <c r="C190" s="3">
-        <v>849</v>
+        <v>659</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3227,7 +3227,7 @@
         <v>209</v>
       </c>
       <c r="C192" s="3">
-        <v>559</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -3238,7 +3238,7 @@
         <v>87</v>
       </c>
       <c r="C193" s="3">
-        <v>5449</v>
+        <v>5439</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3249,7 +3249,7 @@
         <v>210</v>
       </c>
       <c r="C194" s="3">
-        <v>1950</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3260,7 +3260,7 @@
         <v>211</v>
       </c>
       <c r="C195" s="3">
-        <v>910</v>
+        <v>880</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3304,7 +3304,7 @@
         <v>213</v>
       </c>
       <c r="C199" s="3">
-        <v>8509</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -3315,7 +3315,7 @@
         <v>214</v>
       </c>
       <c r="C200" s="3">
-        <v>7859</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -3337,7 +3337,7 @@
         <v>216</v>
       </c>
       <c r="C202" s="3">
-        <v>4330</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3392,7 +3392,7 @@
         <v>221</v>
       </c>
       <c r="C207" s="3">
-        <v>5170</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -3436,7 +3436,7 @@
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -3458,7 +3458,7 @@
         <v>227</v>
       </c>
       <c r="C213" s="3">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -3469,7 +3469,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>529</v>
+        <v>549</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3502,7 +3502,7 @@
         <v>53</v>
       </c>
       <c r="C217" s="3">
-        <v>1405</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3546,7 +3546,7 @@
         <v>132</v>
       </c>
       <c r="C221" s="3">
-        <v>1940</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -3718,7 +3718,7 @@
         <v>196</v>
       </c>
       <c r="C237" s="3">
-        <v>5149</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -3784,7 +3784,7 @@
         <v>254</v>
       </c>
       <c r="C243" s="3">
-        <v>5189</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -3806,7 +3806,7 @@
         <v>125</v>
       </c>
       <c r="C245" s="3">
-        <v>5054</v>
+        <v>5034</v>
       </c>
     </row>
   </sheetData>

--- a/BAK/inventory.xlsx
+++ b/BAK/inventory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="261">
   <si>
     <t>Name</t>
   </si>
@@ -190,7 +190,7 @@
     <t>RELX Infinity 2 Device (7)</t>
   </si>
   <si>
-    <t>2264.0</t>
+    <t>2241.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Device</t>
@@ -220,7 +220,7 @@
     <t>RELX Infinity 2 Plus Device (8)</t>
   </si>
   <si>
-    <t>10409.0</t>
+    <t>10393.0</t>
   </si>
   <si>
     <t>RELX Infinity 2 Plus Device</t>
@@ -292,7 +292,7 @@
     <t>RELX NOVA SILKMESH (25)</t>
   </si>
   <si>
-    <t>44422.0</t>
+    <t>43867.0</t>
   </si>
   <si>
     <t>RELX NOVA SILKMESH</t>
@@ -376,7 +376,7 @@
     <t>RELX Pocket (G01BC) (6)</t>
   </si>
   <si>
-    <t>883.0</t>
+    <t>853.0</t>
   </si>
   <si>
     <t>RELX Pocket (G01BC)</t>
@@ -397,7 +397,7 @@
     <t>RELX Pod Pro 2 (59)</t>
   </si>
   <si>
-    <t>34750.0</t>
+    <t>34150.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2</t>
@@ -580,10 +580,10 @@
     <t>Oolong Ice Tea|高凉铁观音</t>
   </si>
   <si>
-    <t>RELX Pod Pro 2-3 Pods (57)</t>
-  </si>
-  <si>
-    <t>139314.0</t>
+    <t>RELX Pod Pro 2-3 Pods (63)</t>
+  </si>
+  <si>
+    <t>208254.0</t>
   </si>
   <si>
     <t>RELX Pod Pro 2-3 Pods</t>
@@ -592,6 +592,12 @@
     <t>Iced Black Tea|极凉中式红茶</t>
   </si>
   <si>
+    <t>Chocolate mint|巧克力薄荷</t>
+  </si>
+  <si>
+    <t>Coconut Water|椰子水</t>
+  </si>
+  <si>
     <t>Chrysanthemum Ice Tea|菊花茶</t>
   </si>
   <si>
@@ -601,6 +607,9 @@
     <t>Cola Ice|可乐</t>
   </si>
   <si>
+    <t>Classic Tobacco|经典烟草</t>
+  </si>
+  <si>
     <t>Grapefruit Pomegranate|石榴柚子</t>
   </si>
   <si>
@@ -610,6 +619,9 @@
     <t>Green Melon Ice|绿宝石甜瓜</t>
   </si>
   <si>
+    <t>Grape Aloe|芦荟葡萄</t>
+  </si>
+  <si>
     <t>Grape Boom|葡萄[浓]</t>
   </si>
   <si>
@@ -691,6 +703,9 @@
     <t>Pineapple Ice|菠萝</t>
   </si>
   <si>
+    <t>Iced Pocary Sweat|宝矿力</t>
+  </si>
+  <si>
     <t>Pear Loquat|秋月枇杷梨</t>
   </si>
   <si>
@@ -715,6 +730,9 @@
     <t>Tangy Pineapple|酸甜菠萝</t>
   </si>
   <si>
+    <t>Tangerine Splash|三重柑橘</t>
+  </si>
+  <si>
     <t>Thick Taro Scoop|香芋[浓]</t>
   </si>
   <si>
@@ -754,7 +772,7 @@
     <t>Ultra Pod (14)</t>
   </si>
   <si>
-    <t>51505.0</t>
+    <t>47290.0</t>
   </si>
   <si>
     <t>Ultra Pod</t>
@@ -1134,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C245"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="30.7109375" customWidth="1"/>
@@ -1677,7 +1695,7 @@
         <v>61</v>
       </c>
       <c r="C50" s="3">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1721,7 +1739,7 @@
         <v>65</v>
       </c>
       <c r="C54" s="3">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1774,7 +1792,7 @@
         <v>72</v>
       </c>
       <c r="C59" s="3">
-        <v>1275</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1807,7 +1825,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="3">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2034,7 +2052,7 @@
         <v>100</v>
       </c>
       <c r="C83" s="3">
-        <v>1945</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -2045,7 +2063,7 @@
         <v>101</v>
       </c>
       <c r="C84" s="3">
-        <v>3975</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -2067,7 +2085,7 @@
         <v>103</v>
       </c>
       <c r="C86" s="3">
-        <v>1880</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2078,7 +2096,7 @@
         <v>104</v>
       </c>
       <c r="C87" s="3">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -2089,7 +2107,7 @@
         <v>105</v>
       </c>
       <c r="C88" s="3">
-        <v>1404</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -2100,7 +2118,7 @@
         <v>106</v>
       </c>
       <c r="C89" s="3">
-        <v>2325</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -2122,7 +2140,7 @@
         <v>108</v>
       </c>
       <c r="C91" s="3">
-        <v>2744</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -2133,7 +2151,7 @@
         <v>109</v>
       </c>
       <c r="C92" s="3">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -2155,7 +2173,7 @@
         <v>111</v>
       </c>
       <c r="C94" s="3">
-        <v>1420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -2221,7 +2239,7 @@
         <v>117</v>
       </c>
       <c r="C100" s="3">
-        <v>1645</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -2232,7 +2250,7 @@
         <v>118</v>
       </c>
       <c r="C101" s="3">
-        <v>3117</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -2263,7 +2281,7 @@
         <v>41</v>
       </c>
       <c r="C104" s="3">
-        <v>484</v>
+        <v>454</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -2503,7 +2521,7 @@
         <v>145</v>
       </c>
       <c r="C126" s="3">
-        <v>6240</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -2985,7 +3003,7 @@
         <v>191</v>
       </c>
       <c r="C170" s="3">
-        <v>0</v>
+        <v>790</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -2996,7 +3014,7 @@
         <v>149</v>
       </c>
       <c r="C171" s="3">
-        <v>2390</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -3007,7 +3025,7 @@
         <v>192</v>
       </c>
       <c r="C172" s="3">
-        <v>0</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -3018,7 +3036,7 @@
         <v>193</v>
       </c>
       <c r="C173" s="3">
-        <v>1784</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -3029,7 +3047,7 @@
         <v>194</v>
       </c>
       <c r="C174" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -3037,10 +3055,10 @@
         <v>190</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="C175" s="3">
-        <v>0</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -3048,7 +3066,7 @@
         <v>190</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C176" s="3">
         <v>0</v>
@@ -3059,10 +3077,10 @@
         <v>190</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="C177" s="3">
-        <v>2480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -3073,7 +3091,7 @@
         <v>197</v>
       </c>
       <c r="C178" s="3">
-        <v>0</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -3081,10 +3099,10 @@
         <v>190</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="C179" s="3">
-        <v>2050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -3092,10 +3110,10 @@
         <v>190</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C180" s="3">
-        <v>0</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -3103,7 +3121,7 @@
         <v>190</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C181" s="3">
         <v>0</v>
@@ -3114,10 +3132,10 @@
         <v>190</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="C182" s="3">
-        <v>4820</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -3128,7 +3146,7 @@
         <v>201</v>
       </c>
       <c r="C183" s="3">
-        <v>2480</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -3139,7 +3157,7 @@
         <v>202</v>
       </c>
       <c r="C184" s="3">
-        <v>5980</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -3150,7 +3168,7 @@
         <v>203</v>
       </c>
       <c r="C185" s="3">
-        <v>320</v>
+        <v>400</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -3161,7 +3179,7 @@
         <v>204</v>
       </c>
       <c r="C186" s="3">
-        <v>3310</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -3172,7 +3190,7 @@
         <v>205</v>
       </c>
       <c r="C187" s="3">
-        <v>6045</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3183,7 +3201,7 @@
         <v>206</v>
       </c>
       <c r="C188" s="3">
-        <v>1876</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3191,10 +3209,10 @@
         <v>190</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="C189" s="3">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3202,10 +3220,10 @@
         <v>190</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C190" s="3">
-        <v>659</v>
+        <v>8870</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -3213,10 +3231,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C191" s="3">
-        <v>0</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -3224,10 +3242,10 @@
         <v>190</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C192" s="3">
-        <v>439</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -3235,10 +3253,10 @@
         <v>190</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="C193" s="3">
-        <v>5439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -3246,10 +3264,10 @@
         <v>190</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C194" s="3">
-        <v>1810</v>
+        <v>13639</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -3257,10 +3275,10 @@
         <v>190</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C195" s="3">
-        <v>880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -3268,10 +3286,10 @@
         <v>190</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C196" s="3">
-        <v>0</v>
+        <v>419</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -3279,10 +3297,10 @@
         <v>190</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="C197" s="3">
-        <v>0</v>
+        <v>16239</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -3290,10 +3308,10 @@
         <v>190</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="C198" s="3">
-        <v>560</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -3301,10 +3319,10 @@
         <v>190</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C199" s="3">
-        <v>8419</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -3312,10 +3330,10 @@
         <v>190</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C200" s="3">
-        <v>7769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -3323,10 +3341,10 @@
         <v>190</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="C201" s="3">
-        <v>972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3334,10 +3352,10 @@
         <v>190</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>216</v>
+        <v>145</v>
       </c>
       <c r="C202" s="3">
-        <v>4320</v>
+        <v>340</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3348,7 +3366,7 @@
         <v>217</v>
       </c>
       <c r="C203" s="3">
-        <v>8600</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3359,7 +3377,7 @@
         <v>218</v>
       </c>
       <c r="C204" s="3">
-        <v>520</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -3370,7 +3388,7 @@
         <v>219</v>
       </c>
       <c r="C205" s="3">
-        <v>0</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -3381,7 +3399,7 @@
         <v>220</v>
       </c>
       <c r="C206" s="3">
-        <v>10670</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -3392,7 +3410,7 @@
         <v>221</v>
       </c>
       <c r="C207" s="3">
-        <v>5160</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -3403,7 +3421,7 @@
         <v>222</v>
       </c>
       <c r="C208" s="3">
-        <v>4870</v>
+        <v>520</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -3425,7 +3443,7 @@
         <v>224</v>
       </c>
       <c r="C210" s="3">
-        <v>3530</v>
+        <v>10660</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -3436,7 +3454,7 @@
         <v>225</v>
       </c>
       <c r="C211" s="3">
-        <v>80</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -3447,7 +3465,7 @@
         <v>226</v>
       </c>
       <c r="C212" s="3">
-        <v>0</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -3458,7 +3476,7 @@
         <v>227</v>
       </c>
       <c r="C213" s="3">
-        <v>246</v>
+        <v>190</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -3469,7 +3487,7 @@
         <v>228</v>
       </c>
       <c r="C214" s="3">
-        <v>549</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -3491,7 +3509,7 @@
         <v>230</v>
       </c>
       <c r="C216" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -3499,10 +3517,10 @@
         <v>190</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>53</v>
+        <v>231</v>
       </c>
       <c r="C217" s="3">
-        <v>1295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -3510,10 +3528,10 @@
         <v>190</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C218" s="3">
-        <v>3575</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -3521,10 +3539,10 @@
         <v>190</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C219" s="3">
-        <v>6809</v>
+        <v>549</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -3532,10 +3550,10 @@
         <v>190</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C220" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -3543,10 +3561,10 @@
         <v>190</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="C221" s="3">
-        <v>1950</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -3554,10 +3572,10 @@
         <v>190</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="C222" s="3">
-        <v>0</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -3565,10 +3583,10 @@
         <v>190</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C223" s="3">
-        <v>3</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -3576,10 +3594,10 @@
         <v>190</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C224" s="3">
-        <v>9750</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -3587,10 +3605,10 @@
         <v>190</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C225" s="3">
-        <v>7895</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -3598,83 +3616,85 @@
         <v>190</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C226" s="3">
-        <v>8280</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="227" spans="1:3">
-      <c r="A227" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B227" s="2"/>
-      <c r="C227" s="2" t="s">
-        <v>240</v>
+      <c r="A227" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C227" s="3">
+        <v>2350</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C228" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B229" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="C229" s="3">
-        <v>0</v>
+        <v>9463</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C230" s="3">
-        <v>0</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="231" spans="1:3">
-      <c r="A231" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B231" s="2"/>
-      <c r="C231" s="2" t="s">
-        <v>246</v>
+      <c r="A231" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C231" s="3">
+        <v>7895</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="3" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>41</v>
+        <v>244</v>
       </c>
       <c r="C232" s="3">
-        <v>5009</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="233" spans="1:3">
-      <c r="A233" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C233" s="3">
-        <v>0</v>
+      <c r="A233" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -3685,7 +3705,7 @@
         <v>248</v>
       </c>
       <c r="C234" s="3">
-        <v>4834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -3693,10 +3713,10 @@
         <v>247</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="C235" s="3">
-        <v>5264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -3704,109 +3724,173 @@
         <v>247</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="C236" s="3">
-        <v>5404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:3">
-      <c r="A237" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C237" s="3">
-        <v>5139</v>
+      <c r="A237" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>249</v>
+        <v>41</v>
       </c>
       <c r="C238" s="3">
-        <v>0</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="C239" s="3">
-        <v>5119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C240" s="3">
-        <v>0</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="C241" s="3">
-        <v>0</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="C242" s="3">
-        <v>4989</v>
+        <v>4914</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="C243" s="3">
-        <v>5169</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>56</v>
+        <v>255</v>
       </c>
       <c r="C244" s="3">
-        <v>5544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B245" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C245" s="3">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C246" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C247" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C248" s="3">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C249" s="3">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C250" s="3">
+        <v>5154</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B251" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C245" s="3">
-        <v>5034</v>
+      <c r="C251" s="3">
+        <v>4664</v>
       </c>
     </row>
   </sheetData>
